--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6,162,000원</t>
+          <t>6,266,000원</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,906,912원</t>
+          <t>5,999,936원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-255,088원</t>
+          <t>-266,064원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.2%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>744,912원</t>
+          <t>733,936원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-26.6%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>33일</t>
+          <t>35일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>117건</t>
+          <t>121건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.5%</t>
+          <t>-70.4%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,364,096원 → 744,912원 (2026-09-03)</t>
+          <t>2,364,096원 → 699,912원 (2026-09-04)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.8% ~ +26.5%</t>
+          <t>-33.3% ~ +25.6%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-1,471,764원</t>
+          <t>-1,482,740원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1851,6 +1851,62 @@
       </c>
       <c r="H34" t="n">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-45000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>59000</v>
+      </c>
+      <c r="F36" t="n">
+        <v>93024</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34024</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5766779661016949</v>
       </c>
     </row>
   </sheetData>
@@ -1873,8 +1929,8 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1926,25 +1982,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2040816326530612</v>
+        <v>0.196078431372549</v>
       </c>
       <c r="E2" t="n">
-        <v>2567000</v>
+        <v>2612000</v>
       </c>
       <c r="F2" t="n">
         <v>2321139.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-245860.0999999996</v>
+        <v>-290860.0999999996</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.09577721075185026</v>
+        <v>-0.1113553215926492</v>
       </c>
     </row>
     <row r="3">
@@ -1954,25 +2010,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="E3" t="n">
-        <v>3005000</v>
+        <v>3064000</v>
       </c>
       <c r="F3" t="n">
-        <v>2988597.62</v>
+        <v>3081621.62</v>
       </c>
       <c r="G3" t="n">
-        <v>-16402.37999999989</v>
+        <v>17621.62000000011</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.005458362728785321</v>
+        <v>0.005751181462141029</v>
       </c>
     </row>
     <row r="4">
@@ -2014,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2678,6 +2734,44 @@
         <v>744911.9199999999</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>744911.9199999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>699911.9199999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>699911.9199999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>59000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>93024</v>
+      </c>
+      <c r="E36" t="n">
+        <v>733935.9199999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2689,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6365,6 +6459,130 @@
         <v>0</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>피츠버그 vs LA에인절스(핸디캡 LA에인절스 +2.5) + 시애틀 vs 애슬레틱스(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2.584</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>93024</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>LA다저스 vs 워싱턴(핸디캡 워싱턴 +2.5) + 마이애미 vs 시카고컵스(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2.618</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SSG vs 두산(언더오버 언더 10.5) + 롯데 vs 한화(승패 롯데 승)</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2.6896</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>키움 vs NC(언더오버 오버 7.5) + 히로시마 vs 요미우리(승패 히로시마 승)</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E122" t="n">
+        <v>3.5526</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="전체요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="신뢰도" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="운영구간" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="일자별" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="리그별" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="잔고추이" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="베팅내역" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신뢰도" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="운영구간" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일자별" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="리그별" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="잔고추이" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="베팅내역" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
